--- a/docs/sprint2/requirements-defects.xlsx
+++ b/docs/sprint2/requirements-defects.xlsx
@@ -1262,7 +1262,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>«гарантує його доставку до поштової скриньки … не довше ніж за 1 секунду незалежно від поштового провайдера» — доставка залежить від сторонніх поштових серверів, які продукт не контролює.</t>
+          <t>Чек-лист здійсненності (єдиний пункт; виконання залежить від систем, які продукт не контролює): «гарантує його доставку до поштової скриньки … не довше ніж за 1 секунду незалежно від поштового провайдера» — доставка залежить від сторонніх поштових серверів, які продукт не контролює.</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>«не менше 8K (7680×4320) без стиснення … не довше ніж за 50 мс кожне за будь-якого з'єднання» — нестиснене 8K-зображення ≈ 100 МБ, за 50 мс фізично недосяжно навіть на гігабітному каналі.</t>
+          <t>Чек-лист здійсненності (єдиний пункт; фізичні обмеження): «не менше 8K (7680×4320) без стиснення … не довше ніж за 50 мс кожне за будь-якого з'єднання» — нестиснене 8K-зображення ≈ 100 МБ, за 50 мс фізично недосяжно навіть на гігабітному каналі.</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>«перевіряє, що цей код не було використано у жодному іншому інтернет-магазині, зокрема сторонніх» — доступу до даних сторонніх магазинів немає; модуль за 2.3 — бібліотека без зовнішніх залежностей.</t>
+          <t>Чек-лист здійсненності (єдиний пункт; залежність від систем, які продукт не контролює, і обмеження 2.3): «перевіряє, що цей код не було використано у жодному іншому інтернет-магазині, зокрема сторонніх» — доступу до даних сторонніх магазинів немає; модуль за 2.3 — бібліотека без зовнішніх залежностей.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>«не довше ніж за 0,1 с за будь-якого з'єднання з Інтернетом і на будь-якому пристрої» — недосяжно для повільних з'єднань (2G, супутник) і слабких пристроїв.</t>
+          <t>Чек-лист здійсненності (єдиний пункт; технологічно недосяжно): «не довше ніж за 0,1 с за будь-якого з'єднання з Інтернетом і на будь-якому пристрої» — недосяжно для повільних з'єднань (2G, супутник) і слабких пристроїв.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>«додає товар у кошик … миттєво і без помилок» — «миттєво», «без помилок» не дають критерію «пройдено / не пройдено».</t>
+          <t>Тестопридатність, практичний тест (немає числа і способу спостереження; слова-маркери «миттєво», «без помилок»): «додає товар у кошик … миттєво і без помилок» — «миттєво», «без помилок» не дають критерію «пройдено / не пройдено».</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>«Кольорова схема … приємною і сучасною, а шрифти — легкими для читання» — суб'єктивні оцінки, спостережуваного критерію немає.</t>
+          <t>Тестопридатність, практичний тест (немає числа і способу спостереження; суб'єктивні оцінки «приємною», «легкими для читання»): «Кольорова схема … приємною і сучасною, а шрифти — легкими для читання» — суб'єктивні оцінки, спостережуваного критерію немає.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>«Дані покупців надійно захищені, а система не містить вразливостей» — класична неперевірювана вимога: відсутність усіх вразливостей довести неможливо.</t>
+          <t>Тестопридатність, практичний тест (класична неперевірювана вимога; слово-маркер «надійно»): «Дані покупців надійно захищені, а система не містить вразливостей» — класична неперевірювана вимога: відсутність усіх вразливостей довести неможливо.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>«Інтерфейс є інтуїтивно зрозумілим і зручним для всіх категорій користувачів» — слова-маркери «інтуїтивно», «зручно», критерію немає.</t>
+          <t>Тестопридатність, практичний тест (слова-маркери «інтуїтивно», «зручно»): «Інтерфейс є інтуїтивно зрозумілим і зручним для всіх категорій користувачів» — слова-маркери «інтуїтивно», «зручно», критерію немає.</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
